--- a/static/uploads/mau/hopdong/nt1/duoi_o2/hdvth.xlsx
+++ b/static/uploads/mau/hopdong/nt1/duoi_o2/hdvth.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DAT\Desktop\code\working\HRM\static\uploads\mau\hopdong\nt1\duoi_o2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DTD\Code\HRM\static\uploads\mau\hopdong\nt1\duoi_o2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F3F4A0-AF38-45D4-9411-85D251D93E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C234A3-ED67-48DE-B437-3FD5C93EEB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MẪU IN HỢP ĐỒNG LAO ĐỘNG" sheetId="2" r:id="rId1"/>
@@ -487,14 +487,14 @@
     <t>Nếu người lao động không còn tiếp tục làm việc hoặc có đơn xin nghỉ việc đến ngày phát thưởng thì sẽ không được lĩnh thưởng_x000D_.</t>
   </si>
   <si>
-    <t>Địa chỉ: TDP 7 - Thuỷ Đường - Thuỷ Nguyên - Hải Phòng
+    <t>- Địa điểm làm việc: + Tổ dân phố 7, Phường Thủy Nguyên, TP Hải Phòng</t>
+  </si>
+  <si>
+    <t>Địa chỉ: TDP 7 - Thuỷ Nguyên - Hải Phòng
 ĐT: 02253.642.408</t>
   </si>
   <si>
-    <t>Tổ dân phố 7, Phường Thủy Đường, TP Thủy Nguyên, TP Hải Phòng</t>
-  </si>
-  <si>
-    <t>- Địa điểm làm việc: + Tổ dân phố 7, Phường Thủy Đường, TP Thủy Nguyên, TP Hải Phòng</t>
+    <t>Tổ dân phố 7, Phường Thủy Nguyên, TP Hải Phòng</t>
   </si>
 </sst>
 </file>
@@ -1137,17 +1137,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:X138"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="4" customWidth="1"/>
     <col min="9" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="3" customWidth="1"/>
-    <col min="12" max="12" width="3.28515625" customWidth="1"/>
+    <col min="12" max="12" width="3.33203125" customWidth="1"/>
     <col min="13" max="23" width="4" customWidth="1"/>
-    <col min="24" max="24" width="4.5703125" customWidth="1"/>
+    <col min="24" max="24" width="4.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18"/>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1177,13 +1177,13 @@
       <c r="W1" s="19"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
       <c r="E2" s="20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F2" s="21"/>
       <c r="G2" s="21"/>
@@ -1207,7 +1207,7 @@
       <c r="W2" s="13"/>
       <c r="X2" s="13"/>
     </row>
-    <row r="3" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1237,7 +1237,7 @@
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
     </row>
-    <row r="4" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1267,7 +1267,7 @@
       <c r="W4" s="6"/>
       <c r="X4" s="6"/>
     </row>
-    <row r="5" spans="1:24" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1293,7 +1293,7 @@
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
     </row>
-    <row r="6" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>6</v>
       </c>
@@ -1321,7 +1321,7 @@
       <c r="W6" s="16"/>
       <c r="X6" s="16"/>
     </row>
-    <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>7</v>
       </c>
@@ -1349,7 +1349,7 @@
       <c r="W7" s="17"/>
       <c r="X7" s="17"/>
     </row>
-    <row r="8" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1375,7 +1375,7 @@
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
     </row>
-    <row r="9" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="7" t="s">
         <v>8</v>
@@ -1403,7 +1403,7 @@
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
     </row>
-    <row r="10" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="4" t="s">
         <v>9</v>
@@ -1437,7 +1437,7 @@
       <c r="W10" s="7"/>
       <c r="X10" s="7"/>
     </row>
-    <row r="11" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="4" t="s">
         <v>13</v>
@@ -1471,7 +1471,7 @@
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
     </row>
-    <row r="12" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="4" t="s">
         <v>17</v>
@@ -1501,7 +1501,7 @@
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
     </row>
-    <row r="13" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="4" t="s">
         <v>19</v>
@@ -1539,7 +1539,7 @@
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
     </row>
-    <row r="14" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="4" t="s">
         <v>25</v>
@@ -1569,14 +1569,14 @@
       <c r="W14" s="7"/>
       <c r="X14" s="7"/>
     </row>
-    <row r="15" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -1599,7 +1599,7 @@
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
     </row>
-    <row r="16" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="4" t="s">
         <v>27</v>
@@ -1633,7 +1633,7 @@
       <c r="W16" s="14"/>
       <c r="X16" s="14"/>
     </row>
-    <row r="17" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="7" t="s">
         <v>31</v>
@@ -1661,7 +1661,7 @@
       <c r="W17" s="2"/>
       <c r="X17" s="2"/>
     </row>
-    <row r="18" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="4" t="s">
         <v>9</v>
@@ -1695,7 +1695,7 @@
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
     </row>
-    <row r="19" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="4" t="s">
         <v>15</v>
@@ -1729,7 +1729,7 @@
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
     </row>
-    <row r="20" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="4" t="s">
         <v>17</v>
@@ -1759,7 +1759,7 @@
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
     </row>
-    <row r="21" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="4" t="s">
         <v>38</v>
@@ -1795,7 +1795,7 @@
       <c r="W21" s="4"/>
       <c r="X21" s="4"/>
     </row>
-    <row r="22" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="4" t="s">
         <v>27</v>
@@ -1823,7 +1823,7 @@
       <c r="W22" s="2"/>
       <c r="X22" s="2"/>
     </row>
-    <row r="23" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="14" t="s">
         <v>40</v>
@@ -1851,7 +1851,7 @@
       <c r="W23" s="14"/>
       <c r="X23" s="14"/>
     </row>
-    <row r="24" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="7" t="s">
         <v>41</v>
@@ -1879,7 +1879,7 @@
       <c r="W24" s="7"/>
       <c r="X24" s="7"/>
     </row>
-    <row r="25" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="4" t="s">
         <v>42</v>
@@ -1909,7 +1909,7 @@
       <c r="W25" s="4"/>
       <c r="X25" s="4"/>
     </row>
-    <row r="26" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="4" t="s">
         <v>43</v>
@@ -1937,10 +1937,10 @@
       <c r="W26" s="4"/>
       <c r="X26" s="2"/>
     </row>
-    <row r="27" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -1965,7 +1965,7 @@
       <c r="W27" s="4"/>
       <c r="X27" s="4"/>
     </row>
-    <row r="28" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1993,7 +1993,7 @@
       <c r="W28" s="4"/>
       <c r="X28" s="4"/>
     </row>
-    <row r="29" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="4" t="s">
         <v>45</v>
@@ -2023,7 +2023,7 @@
       <c r="W29" s="11"/>
       <c r="X29" s="11"/>
     </row>
-    <row r="30" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="4" t="s">
         <v>47</v>
@@ -2053,7 +2053,7 @@
       <c r="W30" s="4"/>
       <c r="X30" s="4"/>
     </row>
-    <row r="31" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="4" t="s">
         <v>49</v>
@@ -2081,7 +2081,7 @@
       <c r="W31" s="4"/>
       <c r="X31" s="4"/>
     </row>
-    <row r="32" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="7" t="s">
         <v>50</v>
@@ -2109,7 +2109,7 @@
       <c r="W32" s="7"/>
       <c r="X32" s="7"/>
     </row>
-    <row r="33" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="4" t="s">
         <v>51</v>
@@ -2137,7 +2137,7 @@
       <c r="W33" s="4"/>
       <c r="X33" s="4"/>
     </row>
-    <row r="34" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="4" t="s">
         <v>52</v>
@@ -2165,7 +2165,7 @@
       <c r="W34" s="4"/>
       <c r="X34" s="4"/>
     </row>
-    <row r="35" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="4" t="s">
         <v>53</v>
@@ -2193,7 +2193,7 @@
       <c r="W35" s="4"/>
       <c r="X35" s="4"/>
     </row>
-    <row r="36" spans="1:24" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2219,7 +2219,7 @@
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
     </row>
-    <row r="37" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="7" t="s">
         <v>54</v>
@@ -2247,7 +2247,7 @@
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
     </row>
-    <row r="38" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="8" t="s">
         <v>55</v>
@@ -2275,7 +2275,7 @@
       <c r="W38" s="8"/>
       <c r="X38" s="8"/>
     </row>
-    <row r="39" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="7" t="s">
         <v>56</v>
@@ -2305,7 +2305,7 @@
       <c r="W39" s="11"/>
       <c r="X39" s="11"/>
     </row>
-    <row r="40" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="12" t="s">
         <v>58</v>
@@ -2333,7 +2333,7 @@
       <c r="W40" s="13"/>
       <c r="X40" s="13"/>
     </row>
-    <row r="41" spans="1:24" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -2359,7 +2359,7 @@
       <c r="W41" s="2"/>
       <c r="X41" s="2"/>
     </row>
-    <row r="42" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="7" t="s">
         <v>59</v>
@@ -2389,7 +2389,7 @@
       <c r="W42" s="4"/>
       <c r="X42" s="4"/>
     </row>
-    <row r="43" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="4" t="s">
         <v>61</v>
@@ -2417,7 +2417,7 @@
       <c r="W43" s="4"/>
       <c r="X43" s="4"/>
     </row>
-    <row r="44" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="4" t="s">
         <v>62</v>
@@ -2445,7 +2445,7 @@
       <c r="W44" s="4"/>
       <c r="X44" s="4"/>
     </row>
-    <row r="45" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="7" t="s">
         <v>63</v>
@@ -2473,7 +2473,7 @@
       <c r="W45" s="2"/>
       <c r="X45" s="2"/>
     </row>
-    <row r="46" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="7" t="s">
         <v>64</v>
@@ -2501,7 +2501,7 @@
       <c r="W46" s="7"/>
       <c r="X46" s="7"/>
     </row>
-    <row r="47" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="4" t="s">
         <v>153</v>
@@ -2529,7 +2529,7 @@
       <c r="W47" s="4"/>
       <c r="X47" s="4"/>
     </row>
-    <row r="48" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="10" t="s">
         <v>154</v>
@@ -2557,7 +2557,7 @@
       <c r="W48" s="4"/>
       <c r="X48" s="4"/>
     </row>
-    <row r="49" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="7" t="s">
         <v>65</v>
@@ -2587,7 +2587,7 @@
       <c r="W49" s="4"/>
       <c r="X49" s="4"/>
     </row>
-    <row r="50" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="4" t="s">
         <v>67</v>
@@ -2615,7 +2615,7 @@
       <c r="W50" s="4"/>
       <c r="X50" s="2"/>
     </row>
-    <row r="51" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="7" t="s">
         <v>68</v>
@@ -2643,7 +2643,7 @@
       <c r="W51" s="2"/>
       <c r="X51" s="2"/>
     </row>
-    <row r="52" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="4" t="s">
         <v>69</v>
@@ -2671,7 +2671,7 @@
       <c r="W52" s="4"/>
       <c r="X52" s="4"/>
     </row>
-    <row r="53" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="4" t="s">
         <v>70</v>
@@ -2699,7 +2699,7 @@
       <c r="W53" s="4"/>
       <c r="X53" s="4"/>
     </row>
-    <row r="54" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="7" t="s">
         <v>71</v>
@@ -2727,7 +2727,7 @@
       <c r="W54" s="2"/>
       <c r="X54" s="2"/>
     </row>
-    <row r="55" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="4" t="s">
         <v>72</v>
@@ -2755,7 +2755,7 @@
       <c r="W55" s="4"/>
       <c r="X55" s="4"/>
     </row>
-    <row r="56" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="4" t="s">
         <v>73</v>
@@ -2783,7 +2783,7 @@
       <c r="W56" s="4"/>
       <c r="X56" s="4"/>
     </row>
-    <row r="57" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="4" t="s">
         <v>74</v>
@@ -2811,7 +2811,7 @@
       <c r="W57" s="4"/>
       <c r="X57" s="4"/>
     </row>
-    <row r="58" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="7" t="s">
         <v>75</v>
@@ -2839,7 +2839,7 @@
       <c r="W58" s="7"/>
       <c r="X58" s="7"/>
     </row>
-    <row r="59" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="4" t="s">
         <v>76</v>
@@ -2867,7 +2867,7 @@
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
     </row>
-    <row r="60" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="4" t="s">
         <v>77</v>
@@ -2895,7 +2895,7 @@
       <c r="W60" s="4"/>
       <c r="X60" s="4"/>
     </row>
-    <row r="61" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="4" t="s">
         <v>78</v>
@@ -2923,7 +2923,7 @@
       <c r="W61" s="4"/>
       <c r="X61" s="4"/>
     </row>
-    <row r="62" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="4" t="s">
         <v>152</v>
@@ -2951,7 +2951,7 @@
       <c r="W62" s="4"/>
       <c r="X62" s="4"/>
     </row>
-    <row r="63" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="7" t="s">
         <v>79</v>
@@ -2979,7 +2979,7 @@
       <c r="W63" s="7"/>
       <c r="X63" s="7"/>
     </row>
-    <row r="64" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="4" t="s">
         <v>80</v>
@@ -3007,7 +3007,7 @@
       <c r="W64" s="4"/>
       <c r="X64" s="4"/>
     </row>
-    <row r="65" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="9" t="s">
         <v>81</v>
@@ -3035,7 +3035,7 @@
       <c r="W65" s="7"/>
       <c r="X65" s="7"/>
     </row>
-    <row r="66" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="7" t="s">
         <v>82</v>
@@ -3063,7 +3063,7 @@
       <c r="W66" s="7"/>
       <c r="X66" s="7"/>
     </row>
-    <row r="67" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="4" t="s">
         <v>83</v>
@@ -3091,7 +3091,7 @@
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
     </row>
-    <row r="68" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="4" t="s">
         <v>151</v>
@@ -3119,7 +3119,7 @@
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
     </row>
-    <row r="69" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="7" t="s">
         <v>84</v>
@@ -3147,7 +3147,7 @@
       <c r="W69" s="7"/>
       <c r="X69" s="7"/>
     </row>
-    <row r="70" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="4" t="s">
         <v>85</v>
@@ -3175,7 +3175,7 @@
       <c r="W70" s="4"/>
       <c r="X70" s="4"/>
     </row>
-    <row r="71" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="7" t="s">
         <v>149</v>
@@ -3203,7 +3203,7 @@
       <c r="W71" s="7"/>
       <c r="X71" s="7"/>
     </row>
-    <row r="72" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="7" t="s">
         <v>86</v>
@@ -3231,7 +3231,7 @@
       <c r="W72" s="7"/>
       <c r="X72" s="7"/>
     </row>
-    <row r="73" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="4" t="s">
         <v>87</v>
@@ -3259,7 +3259,7 @@
       <c r="W73" s="4"/>
       <c r="X73" s="4"/>
     </row>
-    <row r="74" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="4" t="s">
         <v>88</v>
@@ -3287,7 +3287,7 @@
       <c r="W74" s="4"/>
       <c r="X74" s="4"/>
     </row>
-    <row r="75" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="4" t="s">
         <v>89</v>
@@ -3315,7 +3315,7 @@
       <c r="W75" s="4"/>
       <c r="X75" s="4"/>
     </row>
-    <row r="76" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="4" t="s">
         <v>90</v>
@@ -3343,7 +3343,7 @@
       <c r="W76" s="4"/>
       <c r="X76" s="2"/>
     </row>
-    <row r="77" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="4" t="s">
         <v>91</v>
@@ -3371,7 +3371,7 @@
       <c r="W77" s="4"/>
       <c r="X77" s="4"/>
     </row>
-    <row r="78" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="4" t="s">
         <v>92</v>
@@ -3399,7 +3399,7 @@
       <c r="W78" s="4"/>
       <c r="X78" s="4"/>
     </row>
-    <row r="79" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="4" t="s">
         <v>93</v>
@@ -3427,7 +3427,7 @@
       <c r="W79" s="4"/>
       <c r="X79" s="4"/>
     </row>
-    <row r="80" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="4" t="s">
         <v>94</v>
@@ -3455,7 +3455,7 @@
       <c r="W80" s="4"/>
       <c r="X80" s="4"/>
     </row>
-    <row r="81" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="4" t="s">
         <v>95</v>
@@ -3483,7 +3483,7 @@
       <c r="W81" s="4"/>
       <c r="X81" s="4"/>
     </row>
-    <row r="82" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="8" t="s">
         <v>96</v>
@@ -3511,7 +3511,7 @@
       <c r="W82" s="8"/>
       <c r="X82" s="8"/>
     </row>
-    <row r="83" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="4" t="s">
         <v>97</v>
@@ -3539,7 +3539,7 @@
       <c r="W83" s="4"/>
       <c r="X83" s="4"/>
     </row>
-    <row r="84" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="4" t="s">
         <v>98</v>
@@ -3567,7 +3567,7 @@
       <c r="W84" s="4"/>
       <c r="X84" s="4"/>
     </row>
-    <row r="85" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="4" t="s">
         <v>99</v>
@@ -3595,7 +3595,7 @@
       <c r="W85" s="4"/>
       <c r="X85" s="4"/>
     </row>
-    <row r="86" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="4" t="s">
         <v>100</v>
@@ -3623,7 +3623,7 @@
       <c r="W86" s="4"/>
       <c r="X86" s="4"/>
     </row>
-    <row r="87" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="4" t="s">
         <v>101</v>
@@ -3651,7 +3651,7 @@
       <c r="W87" s="4"/>
       <c r="X87" s="4"/>
     </row>
-    <row r="88" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="4" t="s">
         <v>102</v>
@@ -3679,7 +3679,7 @@
       <c r="W88" s="4"/>
       <c r="X88" s="4"/>
     </row>
-    <row r="89" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="4" t="s">
         <v>103</v>
@@ -3707,7 +3707,7 @@
       <c r="W89" s="4"/>
       <c r="X89" s="4"/>
     </row>
-    <row r="90" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="4" t="s">
         <v>104</v>
@@ -3735,7 +3735,7 @@
       <c r="W90" s="4"/>
       <c r="X90" s="4"/>
     </row>
-    <row r="91" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="4" t="s">
         <v>105</v>
@@ -3763,7 +3763,7 @@
       <c r="W91" s="4"/>
       <c r="X91" s="4"/>
     </row>
-    <row r="92" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="4" t="s">
         <v>106</v>
@@ -3791,7 +3791,7 @@
       <c r="W92" s="4"/>
       <c r="X92" s="4"/>
     </row>
-    <row r="93" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="4" t="s">
         <v>107</v>
@@ -3819,7 +3819,7 @@
       <c r="W93" s="4"/>
       <c r="X93" s="4"/>
     </row>
-    <row r="94" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="4" t="s">
         <v>108</v>
@@ -3847,7 +3847,7 @@
       <c r="W94" s="4"/>
       <c r="X94" s="4"/>
     </row>
-    <row r="95" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="4" t="s">
         <v>109</v>
@@ -3875,7 +3875,7 @@
       <c r="W95" s="4"/>
       <c r="X95" s="4"/>
     </row>
-    <row r="96" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="4" t="s">
         <v>110</v>
@@ -3903,7 +3903,7 @@
       <c r="W96" s="4"/>
       <c r="X96" s="4"/>
     </row>
-    <row r="97" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="4" t="s">
         <v>111</v>
@@ -3931,7 +3931,7 @@
       <c r="W97" s="4"/>
       <c r="X97" s="4"/>
     </row>
-    <row r="98" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="4" t="s">
         <v>112</v>
@@ -3959,7 +3959,7 @@
       <c r="W98" s="4"/>
       <c r="X98" s="4"/>
     </row>
-    <row r="99" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="4" t="s">
         <v>113</v>
@@ -3987,7 +3987,7 @@
       <c r="W99" s="4"/>
       <c r="X99" s="4"/>
     </row>
-    <row r="100" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="4" t="s">
         <v>114</v>
@@ -4015,7 +4015,7 @@
       <c r="W100" s="4"/>
       <c r="X100" s="4"/>
     </row>
-    <row r="101" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="4" t="s">
         <v>115</v>
@@ -4043,7 +4043,7 @@
       <c r="W101" s="4"/>
       <c r="X101" s="4"/>
     </row>
-    <row r="102" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="4" t="s">
         <v>116</v>
@@ -4071,7 +4071,7 @@
       <c r="W102" s="4"/>
       <c r="X102" s="4"/>
     </row>
-    <row r="103" spans="1:24" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:24" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -4097,7 +4097,7 @@
       <c r="W103" s="2"/>
       <c r="X103" s="2"/>
     </row>
-    <row r="104" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="7" t="s">
         <v>117</v>
@@ -4125,7 +4125,7 @@
       <c r="W104" s="7"/>
       <c r="X104" s="7"/>
     </row>
-    <row r="105" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="7" t="s">
         <v>118</v>
@@ -4153,7 +4153,7 @@
       <c r="W105" s="7"/>
       <c r="X105" s="7"/>
     </row>
-    <row r="106" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="4" t="s">
         <v>119</v>
@@ -4181,7 +4181,7 @@
       <c r="W106" s="4"/>
       <c r="X106" s="4"/>
     </row>
-    <row r="107" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="4" t="s">
         <v>120</v>
@@ -4209,7 +4209,7 @@
       <c r="W107" s="4"/>
       <c r="X107" s="4"/>
     </row>
-    <row r="108" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="4" t="s">
         <v>121</v>
@@ -4237,7 +4237,7 @@
       <c r="W108" s="4"/>
       <c r="X108" s="4"/>
     </row>
-    <row r="109" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="4" t="s">
         <v>122</v>
@@ -4265,7 +4265,7 @@
       <c r="W109" s="4"/>
       <c r="X109" s="4"/>
     </row>
-    <row r="110" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="4" t="s">
         <v>123</v>
@@ -4293,7 +4293,7 @@
       <c r="W110" s="4"/>
       <c r="X110" s="4"/>
     </row>
-    <row r="111" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="7" t="s">
         <v>124</v>
@@ -4321,7 +4321,7 @@
       <c r="W111" s="7"/>
       <c r="X111" s="7"/>
     </row>
-    <row r="112" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="4" t="s">
         <v>125</v>
@@ -4349,7 +4349,7 @@
       <c r="W112" s="4"/>
       <c r="X112" s="4"/>
     </row>
-    <row r="113" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="4" t="s">
         <v>126</v>
@@ -4377,7 +4377,7 @@
       <c r="W113" s="4"/>
       <c r="X113" s="4"/>
     </row>
-    <row r="114" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="4" t="s">
         <v>127</v>
@@ -4405,7 +4405,7 @@
       <c r="W114" s="4"/>
       <c r="X114" s="4"/>
     </row>
-    <row r="115" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="4" t="s">
         <v>128</v>
@@ -4433,7 +4433,7 @@
       <c r="W115" s="4"/>
       <c r="X115" s="4"/>
     </row>
-    <row r="116" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="7" t="s">
         <v>129</v>
@@ -4461,7 +4461,7 @@
       <c r="W116" s="7"/>
       <c r="X116" s="7"/>
     </row>
-    <row r="117" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="4" t="s">
         <v>130</v>
@@ -4489,7 +4489,7 @@
       <c r="W117" s="4"/>
       <c r="X117" s="4"/>
     </row>
-    <row r="118" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="4" t="s">
         <v>131</v>
@@ -4517,7 +4517,7 @@
       <c r="W118" s="4"/>
       <c r="X118" s="4"/>
     </row>
-    <row r="119" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="4" t="s">
         <v>132</v>
@@ -4545,7 +4545,7 @@
       <c r="W119" s="4"/>
       <c r="X119" s="4"/>
     </row>
-    <row r="120" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="4" t="s">
         <v>133</v>
@@ -4573,7 +4573,7 @@
       <c r="W120" s="4"/>
       <c r="X120" s="4"/>
     </row>
-    <row r="121" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="4" t="s">
         <v>134</v>
@@ -4601,7 +4601,7 @@
       <c r="W121" s="4"/>
       <c r="X121" s="4"/>
     </row>
-    <row r="122" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="4" t="s">
         <v>135</v>
@@ -4629,7 +4629,7 @@
       <c r="W122" s="4"/>
       <c r="X122" s="4"/>
     </row>
-    <row r="123" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="7" t="s">
         <v>136</v>
@@ -4657,7 +4657,7 @@
       <c r="W123" s="7"/>
       <c r="X123" s="7"/>
     </row>
-    <row r="124" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="4" t="s">
         <v>137</v>
@@ -4685,7 +4685,7 @@
       <c r="W124" s="4"/>
       <c r="X124" s="4"/>
     </row>
-    <row r="125" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="4" t="s">
         <v>138</v>
@@ -4713,7 +4713,7 @@
       <c r="W125" s="4"/>
       <c r="X125" s="4"/>
     </row>
-    <row r="126" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="4" t="s">
         <v>139</v>
@@ -4741,7 +4741,7 @@
       <c r="W126" s="4"/>
       <c r="X126" s="4"/>
     </row>
-    <row r="127" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="4" t="s">
         <v>140</v>
@@ -4769,7 +4769,7 @@
       <c r="W127" s="4"/>
       <c r="X127" s="4"/>
     </row>
-    <row r="128" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="4" t="s">
         <v>141</v>
@@ -4797,7 +4797,7 @@
       <c r="W128" s="4"/>
       <c r="X128" s="4"/>
     </row>
-    <row r="129" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="5" t="s">
         <v>142</v>
@@ -4827,7 +4827,7 @@
       <c r="W129" s="5"/>
       <c r="X129" s="5"/>
     </row>
-    <row r="130" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="6" t="s">
         <v>144</v>
@@ -4855,7 +4855,7 @@
       <c r="W130" s="6"/>
       <c r="X130" s="6"/>
     </row>
-    <row r="131" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -4881,7 +4881,7 @@
       <c r="W131" s="2"/>
       <c r="X131" s="2"/>
     </row>
-    <row r="132" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -4907,7 +4907,7 @@
       <c r="W132" s="2"/>
       <c r="X132" s="2"/>
     </row>
-    <row r="133" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -4933,7 +4933,7 @@
       <c r="W133" s="2"/>
       <c r="X133" s="2"/>
     </row>
-    <row r="134" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -4959,7 +4959,7 @@
       <c r="W134" s="2"/>
       <c r="X134" s="2"/>
     </row>
-    <row r="135" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -4989,7 +4989,7 @@
       <c r="W135" s="4"/>
       <c r="X135" s="4"/>
     </row>
-    <row r="136" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -5017,7 +5017,7 @@
       <c r="W136" s="4"/>
       <c r="X136" s="2"/>
     </row>
-    <row r="137" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -5047,7 +5047,7 @@
       <c r="W137" s="2"/>
       <c r="X137" s="2"/>
     </row>
-    <row r="138" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
